--- a/artfynd/A 36484-2024 artfynd.xlsx
+++ b/artfynd/A 36484-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129166198</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129166196</v>
       </c>
       <c r="B3" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36484-2024 artfynd.xlsx
+++ b/artfynd/A 36484-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129166198</v>
       </c>
       <c r="B2" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129166196</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36484-2024 artfynd.xlsx
+++ b/artfynd/A 36484-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129166198</v>
       </c>
       <c r="B2" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129166196</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
